--- a/Rock Spring Rd Property - Administrative/~Rock Springs Property Expenses.xlsx
+++ b/Rock Spring Rd Property - Administrative/~Rock Springs Property Expenses.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\The_Fort\Rock Spring Rd Property - Administrative\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LeopardPaul\Dev\The-Fort\Rock Spring Rd Property - Administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A24AA301-403B-4A6B-BFFD-8A09316B12CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB645BAB-B6D0-4042-9769-BFF3BBBFD4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7790" yWindow="2790" windowWidth="28800" windowHeight="15370" xr2:uid="{3BC15B69-BB54-4737-9A94-1FFB276CBE32}"/>
+    <workbookView xWindow="3240" yWindow="4245" windowWidth="28800" windowHeight="15345" xr2:uid="{3BC15B69-BB54-4737-9A94-1FFB276CBE32}"/>
   </bookViews>
   <sheets>
     <sheet name="rsp" sheetId="1" r:id="rId1"/>
@@ -1235,22 +1235,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21704222-709A-4140-B2A3-7D6A04707F2E}">
   <dimension ref="B2:F34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.1796875" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" customWidth="1"/>
-    <col min="3" max="3" width="39.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="52.26953125" customWidth="1"/>
-    <col min="6" max="6" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" customWidth="1"/>
+    <col min="3" max="3" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.28515625" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="40" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1258,13 +1258,13 @@
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="F3" s="13">
         <f>SUM(HistoryTable3[Amount])</f>
         <v>271292.76000000007</v>
       </c>
     </row>
-    <row r="4" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="7">
         <v>45951</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="7">
         <v>45959</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>174.4</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="7">
         <v>45965</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>264373.62</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="7">
         <v>45965</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="7">
         <v>45967</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>115.53</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="7">
         <v>45968</v>
       </c>
@@ -1383,7 +1383,7 @@
         <v>48.57</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="7">
         <v>45969</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>10.79</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="7">
         <v>45969</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>104.99</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="7">
         <v>45969</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>808.71</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="7">
         <v>45981</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="7">
         <v>45992</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="7">
         <v>45992</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="7">
         <v>45992</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>151.94999999999999</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="7">
         <v>46000</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>141.69</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B19" s="7">
         <v>46001</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="7"/>
       <c r="C20" s="8" t="s">
         <v>34</v>
@@ -1551,7 +1551,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="7">
         <v>46002</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>51.81</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="7">
         <v>46019</v>
       </c>
@@ -1585,84 +1585,84 @@
         <v>9.9499999999999993</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="7"/>
       <c r="C23" s="8"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="7"/>
       <c r="C24" s="8"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="10"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="7"/>
       <c r="C25" s="8"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="10"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="7"/>
       <c r="C26" s="8"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="10"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="7"/>
       <c r="C27" s="8"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="10"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="7"/>
       <c r="C28" s="8"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="10"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="7"/>
       <c r="C29" s="8"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="10"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="10"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="7"/>
       <c r="C31" s="8"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="10"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="7"/>
       <c r="C32" s="8"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="10"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="7"/>
       <c r="C33" s="8"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="10"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="7"/>
       <c r="C34" s="8"/>
       <c r="D34" s="9"/>
@@ -1689,5 +1689,6 @@
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{3a1c331b-5232-43a0-827b-34eef4b3955f}" enabled="1" method="Privileged" siteId="{3701aadf-5391-43be-bb84-25a015a895f5}" contentBits="2" removed="0"/>
+  <clbl:label id="{a5ae83bf-5173-442f-899b-ca1b50b823cd}" enabled="1" method="Privileged" siteId="{81349428-f52e-4686-aac8-448974b80e31}" contentBits="2" removed="0"/>
 </clbl:labelList>
 </file>
--- a/Rock Spring Rd Property - Administrative/~Rock Springs Property Expenses.xlsx
+++ b/Rock Spring Rd Property - Administrative/~Rock Springs Property Expenses.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LeopardPaul\Dev\The-Fort\Rock Spring Rd Property - Administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB645BAB-B6D0-4042-9769-BFF3BBBFD4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C571803A-51C4-4740-A8FD-295371A8050D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="4245" windowWidth="28800" windowHeight="15345" xr2:uid="{3BC15B69-BB54-4737-9A94-1FFB276CBE32}"/>
+    <workbookView xWindow="1185" yWindow="1785" windowWidth="17610" windowHeight="15345" xr2:uid="{3BC15B69-BB54-4737-9A94-1FFB276CBE32}"/>
   </bookViews>
   <sheets>
     <sheet name="rsp" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="56">
   <si>
     <t>Date</t>
   </si>
@@ -150,9 +150,6 @@
     <t>Amazon</t>
   </si>
   <si>
-    <t>Otter Wax Leather Salve</t>
-  </si>
-  <si>
     <t>Madison County Address Verification</t>
   </si>
   <si>
@@ -163,6 +160,48 @@
   </si>
   <si>
     <t>Wire transfer fee</t>
+  </si>
+  <si>
+    <t>Survey tape, reflective trail tacks</t>
+  </si>
+  <si>
+    <t>Keter Kenwood 92 gal deck box (x2), tripod plate</t>
+  </si>
+  <si>
+    <t>Fiskars X7 Hatchet + sharpener</t>
+  </si>
+  <si>
+    <t>Tree identification books x2</t>
+  </si>
+  <si>
+    <t>Tree identification book</t>
+  </si>
+  <si>
+    <t>Rustoleum purple paint sprtay 12 oz, 6 pack</t>
+  </si>
+  <si>
+    <t>Toyota Tundra bed cover + install</t>
+  </si>
+  <si>
+    <t>Rocket City Off-Road</t>
+  </si>
+  <si>
+    <t>Onx Maps Elite</t>
+  </si>
+  <si>
+    <t>Spypoint</t>
+  </si>
+  <si>
+    <t>OnxMaps</t>
+  </si>
+  <si>
+    <t>Spypoint Cams full def pics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truck tool box </t>
+  </si>
+  <si>
+    <t>Northern Tool</t>
   </si>
 </sst>
 </file>
@@ -903,8 +942,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CFB29E69-3E6B-47DD-8819-9CE7464E55F0}" name="HistoryTable3" displayName="HistoryTable3" ref="B4:F34" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="B4:F34" xr:uid="{CFB29E69-3E6B-47DD-8819-9CE7464E55F0}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F18">
-    <sortCondition ref="B4:B18"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F34">
+    <sortCondition ref="B4:B34"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{FB27B325-B6DE-4FBB-9E98-81BD11CE29FD}" name="Date" dataDxfId="4"/>
@@ -1241,7 +1280,7 @@
     <col min="2" max="2" width="11.85546875" customWidth="1"/>
     <col min="3" max="3" width="39.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="52.28515625" customWidth="1"/>
+    <col min="5" max="5" width="30.28515625" customWidth="1"/>
     <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1261,7 +1300,7 @@
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="F3" s="13">
         <f>SUM(HistoryTable3[Amount])</f>
-        <v>271292.76000000007</v>
+        <v>272849.67999999993</v>
       </c>
     </row>
     <row r="4" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1337,13 +1376,13 @@
         <v>45965</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F8" s="10">
         <v>25</v>
@@ -1473,7 +1512,7 @@
         <v>45992</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>16</v>
@@ -1490,7 +1529,7 @@
         <v>45992</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>16</v>
@@ -1537,7 +1576,9 @@
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="7"/>
+      <c r="B20" s="7">
+        <v>46001</v>
+      </c>
       <c r="C20" s="8" t="s">
         <v>34</v>
       </c>
@@ -1565,95 +1606,192 @@
         <v>37</v>
       </c>
       <c r="F21" s="10">
-        <v>51.81</v>
+        <v>37.950000000000003</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="7">
-        <v>46019</v>
+        <v>46028</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F22" s="10">
-        <v>9.9499999999999993</v>
+        <v>84.41</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="7"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="10"/>
+      <c r="B23" s="7">
+        <v>46031</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="10">
+        <v>168.23</v>
+      </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="7"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="10"/>
+      <c r="B24" s="7">
+        <v>46036</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="10">
+        <v>57.72</v>
+      </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="7"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="10"/>
+      <c r="B25" s="7">
+        <v>46045</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" s="10">
+        <v>24</v>
+      </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="7"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="10"/>
+      <c r="B26" s="7">
+        <v>46063</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" s="10">
+        <v>6.54</v>
+      </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="7"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="10"/>
+      <c r="B27" s="7">
+        <v>46064</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27" s="10">
+        <v>26.98</v>
+      </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="7"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="10"/>
+      <c r="B28" s="7">
+        <v>46078</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F28" s="10">
+        <f>35.16 + 3.4/2</f>
+        <v>36.86</v>
+      </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="7"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="10"/>
+      <c r="B29" s="7">
+        <v>46078</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F29" s="10">
+        <v>894</v>
+      </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="7"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="10"/>
+      <c r="B30" s="7">
+        <v>46083</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="10">
+        <v>99.99</v>
+      </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="7"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="10"/>
+      <c r="B31" s="7">
+        <v>46090</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="10">
+        <v>32</v>
+      </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="7"/>
-      <c r="C32" s="8"/>
+      <c r="C32" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="10"/>
+      <c r="E32" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F32" s="10">
+        <v>150</v>
+      </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="7"/>
@@ -1670,7 +1808,7 @@
       <c r="F34" s="10"/>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D34" xr:uid="{ED687E50-43FC-43EF-ACFF-CBEB01A1C38F}">
       <formula1>"Reg-Primary,Fid-WROS,Reg-Paul,Reg-Swire,VISA-Amz"</formula1>
     </dataValidation>
